--- a/mappingCorps/ig/FRObservationMicroorganismDetectionLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRObservationMicroorganismDetectionLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="70">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMRechercheDeMicroOrganismes vers le profil CDA FRCDARechercheDeMicroOrganismes, puis vers le profil FHIR FRObservationMicroorganismDetectionDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMMicroOrganismSearch vers le profil CDA FRCDARechercheDeMicroOrganismes, puis vers le profil FHIR FRObservationMicroorganismDetectionDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-recherche-de-micro-organismes</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-micro-organism-search</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-recherche-de-micro-organismes</t>
   </si>
   <si>
-    <t>FRLMRechercheDeMicroOrganismes</t>
+    <t>FRLMMicroOrganismSearch</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,70 +118,112 @@
     <t>FRCDARechercheDeMicroOrganismes</t>
   </si>
   <si>
-    <t>FRLMRechercheDeMicroOrganismes.identifiant</t>
+    <t>FRLMMicroOrganismSearch.header.identifier</t>
   </si>
   <si>
     <t>FRCDARechercheDeMicroOrganismes.id</t>
   </si>
   <si>
-    <t>FRLMRechercheDeMicroOrganismes.code</t>
+    <t>FRLMMicroOrganismSearch.header.subject</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.subject</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.author[x]</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.author</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.performer[x]</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.performer</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.participant[x]</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.participant</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.informant</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.informant</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.date</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.author.time</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.status</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.header.language</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.languageCode</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.observationDate</t>
+  </si>
+  <si>
+    <t>FRCDARechercheDeMicroOrganismes.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMMicroOrganismSearch.type</t>
   </si>
   <si>
     <t>FRCDARechercheDeMicroOrganismes.code</t>
   </si>
   <si>
-    <t>FRLMRechercheDeMicroOrganismes.description</t>
-  </si>
-  <si>
-    <t>FRCDARechercheDeMicroOrganismes.text</t>
-  </si>
-  <si>
-    <t>FRLMRechercheDeMicroOrganismes.statut</t>
-  </si>
-  <si>
-    <t>FRCDARechercheDeMicroOrganismes.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMRechercheDeMicroOrganismes.date</t>
-  </si>
-  <si>
-    <t>FRCDARechercheDeMicroOrganismes.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMRechercheDeMicroOrganismes.valeur</t>
+    <t>FRLMMicroOrganismSearch.result</t>
   </si>
   <si>
     <t>FRCDARechercheDeMicroOrganismes.value</t>
   </si>
   <si>
-    <t>FRLMRechercheDeMicroOrganismes.auteur</t>
-  </si>
-  <si>
-    <t>FRCDARechercheDeMicroOrganismes.author</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-ml-micro-organism-search</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-microorganism-detection-document</t>
   </si>
   <si>
+    <t>FRObservationMicroorganismDetectionDocument</t>
+  </si>
+  <si>
     <t>FRObservationMicroorganismDetectionDocument.identifier</t>
   </si>
   <si>
+    <t>FRObservationMicroorganismDetectionDocument.subject</t>
+  </si>
+  <si>
+    <t>FRObservationMicroorganismDetectionDocument.extension:author</t>
+  </si>
+  <si>
+    <t>FRObservationMicroorganismDetectionDocument.performer</t>
+  </si>
+  <si>
+    <t>FRObservationMicroorganismDetectionDocument.issued</t>
+  </si>
+  <si>
+    <t>FRObservationMicroorganismDetectionDocument.status</t>
+  </si>
+  <si>
+    <t>FRObservationMicroorganismDetectionDocument.language</t>
+  </si>
+  <si>
     <t>FRObservationMicroorganismDetectionDocument.code</t>
   </si>
   <si>
-    <t>FRObservationMicroorganismDetectionDocument.code.text</t>
-  </si>
-  <si>
-    <t>FRObservationMicroorganismDetectionDocument.status</t>
-  </si>
-  <si>
-    <t>FRObservationMicroorganismDetectionDocument.effective[x]</t>
-  </si>
-  <si>
     <t>FRObservationMicroorganismDetectionDocument.valueBoolean</t>
-  </si>
-  <si>
-    <t>FRObservationMicroorganismDetectionDocument.performer.extension:author</t>
   </si>
 </sst>
 </file>
@@ -433,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -573,6 +615,71 @@
         <v>47</v>
       </c>
       <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E15" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -581,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -603,7 +710,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -612,7 +719,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -620,94 +727,159 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
